--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -991,7 +991,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 10:30:30</t>
+          <t>2026-10-14 14:14:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -2937,7 +2937,11 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>( &lt;http://publications.europa.eu/resource/authority/distribution-status/COMPLETED&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/DEVELOP&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/WITHDRAWN&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/PLANNED&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/ARCHIVE&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/ONGOING&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/REQUIRED&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/OP_DATPRO&gt; &lt;http://publications.europa.eu/resource/authority/distribution-status/DEPRECATED&gt; )</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -2949,7 +2953,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>dash:URIEditor</t>
+          <t>dash:EnumSelectEditor</t>
         </is>
       </c>
     </row>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,6 +828,23 @@
       <c r="C25" t="inlineStr">
         <is>
           <t>http://schema.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PREFIX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>hrishapes</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>http://data.health-ri.nl/core/p2/</t>
         </is>
       </c>
     </row>
@@ -853,7 +870,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#aux-DistributionShape</t>
+          <t>http://data.health-ri.nl/core/p2/aux-DistributionShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -991,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:14:48</t>
+          <t>2026-10-14 14:30:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1215,7 +1232,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1282,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#DistributionShape</t>
+          <t>http://data.health-ri.nl/core/p2/DistributionShape</t>
         </is>
       </c>
       <c r="C1" t="inlineStr"/>
@@ -1684,12 +1701,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:accessService</t>
+          <t>hrishapes:DistributionShape#dcat:accessService</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1740,12 +1757,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:accessURL</t>
+          <t>hrishapes:DistributionShape#dcat:accessURL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1802,12 +1819,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcatap:applicableLegislation</t>
+          <t>hrishapes:DistributionShape#dcatap:applicableLegislation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1860,12 +1877,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcatap:availability</t>
+          <t>hrishapes:DistributionShape#dcatap:availability</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1920,12 +1937,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:byteSize</t>
+          <t>hrishapes:DistributionShape#dcat:byteSize</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1984,12 +2001,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/spdx:checksum</t>
+          <t>hrishapes:DistributionShape#spdx:checksum</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2044,12 +2061,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:compressFormat</t>
+          <t>hrishapes:DistributionShape#dcat:compressFormat</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2104,12 +2121,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:description</t>
+          <t>hrishapes:DistributionShape#dct:description</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2164,12 +2181,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/foaf:page</t>
+          <t>hrishapes:DistributionShape#foaf:page</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2222,12 +2239,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:downloadURL</t>
+          <t>hrishapes:DistributionShape#dcat:downloadURL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2282,12 +2299,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:format</t>
+          <t>hrishapes:DistributionShape#dct:format</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2342,12 +2359,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:language</t>
+          <t>hrishapes:DistributionShape#dct:language</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2400,12 +2417,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:license</t>
+          <t>hrishapes:DistributionShape#dct:license</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2462,12 +2479,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:conformsTo</t>
+          <t>hrishapes:DistributionShape#dct:conformsTo</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2520,12 +2537,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:mediaType</t>
+          <t>hrishapes:DistributionShape#dcat:mediaType</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2580,12 +2597,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:modified</t>
+          <t>hrishapes:DistributionShape#dct:modified</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2648,12 +2665,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:packageFormat</t>
+          <t>hrishapes:DistributionShape#dcat:packageFormat</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2708,12 +2725,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:issued</t>
+          <t>hrishapes:DistributionShape#dct:issued</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2776,12 +2793,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/healthdcatap:retentionperiod</t>
+          <t>hrishapes:DistributionShape#healthdcatap:retentionperiod</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2836,12 +2853,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:rights</t>
+          <t>hrishapes:DistributionShape#dct:rights</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2896,12 +2913,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/adms:status</t>
+          <t>hrishapes:DistributionShape#adms:status</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2960,12 +2977,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dcat:temporalResolution</t>
+          <t>hrishapes:DistributionShape#dcat:temporalResolution</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3024,12 +3041,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hri:DistributionShape/dct:title</t>
+          <t>hrishapes:DistributionShape#dct:title</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hri:DistributionShape</t>
+          <t>hrishapes:DistributionShape</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 14:30:38</t>
+          <t>2026-10-19 15:50:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -1729,7 +1729,11 @@
       <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>sh:IRI</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1925,7 +1929,7 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -2033,7 +2037,7 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#ChecksumShape</t>
+          <t>http://data.health-ri.nl/core/p2/ChecksumShape</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -2109,7 +2113,7 @@
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2347,7 +2351,7 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2405,7 +2409,7 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -2585,7 +2589,7 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2713,7 +2717,7 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -2825,7 +2829,7 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://w3id.org/health-ri/metadata-vocabulary#PeriodOfTimeShape</t>
+          <t>http://data.health-ri.nl/core/p2/PeriodOfTimeShape</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2965,7 +2969,7 @@
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>dash:URIViewer</t>
+          <t>dash:LabelViewer</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-19 15:50:03</t>
+          <t>2026-10-26 13:15:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 13:15:50</t>
+          <t>2026-10-26 16:19:38</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-26 16:19:38</t>
+          <t>2026-10-27 15:44:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-27 15:44:13</t>
+          <t>2026-10-28 09:50:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>

--- a/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
+++ b/Formalisation(shacl)/Core/SHACL_pipeline_templates/SHACL-distribution.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-28 09:50:41</t>
+          <t>2026-10-28 11:04:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
